--- a/hisobotlar/Davomat_Jurnali_Uchun_Malumotlar.xlsx
+++ b/hisobotlar/Davomat_Jurnali_Uchun_Malumotlar.xlsx
@@ -689,7 +689,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="J9" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="J11" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K12" s="8" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K14" s="8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K16" s="8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="J19" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K20" s="8" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K26" s="8" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K28" s="8" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K32" s="8" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K34" s="8" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K36" s="8" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K38" s="8" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5301,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/1 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="F27" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5726,7 @@
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       <c r="E34" s="4" t="inlineStr"/>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5943,7 +5943,7 @@
       <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -5993,7 +5993,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="F41" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6039,7 +6039,7 @@
       <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6064,7 +6064,7 @@
       </c>
       <c r="F43" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="F47" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="F49" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6289,7 +6289,7 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       <c r="E54" s="4" t="inlineStr"/>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F57" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="F59" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F61" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       <c r="E63" s="9" t="inlineStr"/>
       <c r="F63" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       <c r="E64" s="4" t="inlineStr"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="F65" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6652,7 +6652,7 @@
       </c>
       <c r="F67" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="F69" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6727,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6773,7 +6773,7 @@
       <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="F75" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7173,7 +7173,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7273,7 @@
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7298,7 +7298,7 @@
       </c>
       <c r="F93" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7398,7 +7398,7 @@
       </c>
       <c r="F97" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="F99" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="F101" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="F103" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="F105" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7619,7 +7619,7 @@
       <c r="E106" s="4" t="inlineStr"/>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="F107" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7694,7 +7694,7 @@
       </c>
       <c r="F109" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="F111" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="F113" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="F117" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="F119" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7969,7 +7969,7 @@
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -7994,7 +7994,7 @@
       </c>
       <c r="F121" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8044,7 +8044,7 @@
       </c>
       <c r="F123" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8069,7 +8069,7 @@
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="F125" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="F129" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="F131" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="F135" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8369,7 +8369,7 @@
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="F139" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       <c r="E141" s="9" t="inlineStr"/>
       <c r="F141" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8515,7 +8515,7 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8540,7 +8540,7 @@
       </c>
       <c r="F143" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="F145" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="F147" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="F149" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8715,7 +8715,7 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="F151" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8765,7 +8765,7 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="F153" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F155" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8890,7 +8890,7 @@
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
       <c r="E158" s="4" t="inlineStr"/>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -8986,7 +8986,7 @@
       </c>
       <c r="F161" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="F163" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="F167" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F169" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       <c r="E170" s="4" t="inlineStr"/>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9228,7 +9228,7 @@
       <c r="E171" s="9" t="inlineStr"/>
       <c r="F171" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9253,7 @@
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
       </c>
       <c r="F173" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="F175" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="F177" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9403,7 +9403,7 @@
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
       <c r="E179" s="9" t="inlineStr"/>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>№ 18, 04.09.2025</t>
+          <t>T-40/2 02.09.2026</t>
         </is>
       </c>
     </row>

--- a/hisobotlar/Davomat_Jurnali_Uchun_Malumotlar.xlsx
+++ b/hisobotlar/Davomat_Jurnali_Uchun_Malumotlar.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guluston, Guluston, 4.0</t>
+          <t>Kitob tumani, Guluston, Guluston, 4-uy</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -717,15 +717,19 @@
           <t>+998 77 062-98-90</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 319-62-60</t>
+        </is>
+      </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Opasi / Singlisi</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Kesh MFY, Kalakon kucha, 91-uy</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -760,27 +764,27 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>+998 88 617-78-60</t>
+          <t>+998 97 619-02-15</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+998 91 457-78-60</t>
+          <t>+998 88 731-19-69</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Pakkandi MFY, Safarabot, 29_uy</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -960,22 +964,22 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>+998 97 335-05-82</t>
+          <t>+998 97 863-50-82</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>+998 97 863-50-82</t>
+          <t>+998 97 355-05-82</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Ukasi</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Yangiqishloq, 44-uy</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -1060,18 +1064,22 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
+          <t>+998 77 864-19-17</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>+998 91 217-43-55</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Turon MFY, Yangi obod, 62-uy</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -1111,17 +1119,17 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>+998 91 815-13-09</t>
+          <t>+998 91 817-20-73</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Saroy koʻchasi, 17-uy</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -1159,15 +1167,19 @@
           <t>+998 88 088-01-24</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 561-30-02</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kotob tumani, Sevaz MFY, Taraqqiyot kuchasi, 130-uy</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1217,7 +1229,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44.0</t>
+          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44-uy</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -1267,7 +1279,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35.0</t>
+          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35-uy</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1538,21 +1550,29 @@
           <t>16.08.2008</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>+998 95 050-54-08</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+998 99 062-62-08</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Qamashi, Yuksalish MFY, Olmazor, 183-uy</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1726,8 +1746,16 @@
           <t>13.11.2008</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -1735,7 +1763,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Qashqadaryo MFY, Minjir qishlogʻi, 51-uy</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -1785,7 +1813,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz Shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
+          <t>Shahrisabz shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -1835,7 +1863,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432.0</t>
+          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432-uy</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -1870,22 +1898,22 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>+998 88 868-99-08</t>
+          <t>+998 88 336-77-74</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>+998 95 770-11-69</t>
+          <t>+998 90 716-31-42</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Shanbe MFY, Shabboda, 35 -uy</t>
+          <t>Shahrisabz shahar, Do'stlik MFY, Bunyodkor ko'chasi, 62/16-uy</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -1923,7 +1951,11 @@
           <t>+998 88 011-58-19</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+998 87 465-05-87</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -1931,7 +1963,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boģbon MFY, Ochamayli kòchasi, 100-uy</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -2131,7 +2163,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84.0</t>
+          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84-uy</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2271,22 +2303,22 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>+998 88 977-06-93</t>
+          <t>+998 99 201-92-74</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Ayoqchi MFY, Qovchin qishlogʻi, 92uy</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -2396,23 +2428,27 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>+998 91 871-57-37</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
+          <t>+998 77 006-91-49</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>+998 90 960-45-80</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Taragʻay MFY, Taragʻay, Yuq</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -2472,14 +2508,10 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>+998 87 636-07-08</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+998 97 636-37-74</t>
-        </is>
-      </c>
+          <t>+998 87 636-07-08 / +998 97 636-37-74 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr"/>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -2632,14 +2664,10 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>+998 88 100-95-04</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+998 97 632-55-74</t>
-        </is>
-      </c>
+          <t>+998 88 100-95-04 / +998 97 632-55-74 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -2672,12 +2700,12 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>+998 77 629-45-08</t>
+          <t>+998 95 740-19-81</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>+998 88 738-19-82</t>
+          <t>+998 95 740-19-81</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -2687,7 +2715,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Toʻdamaydon, Fidokor, 92.0</t>
+          <t>Shahrisabz tumani, Toʻdamaydon, Fidokor, 92-uy</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -2712,12 +2740,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>+998 88 619-97-03</t>
+          <t>+998 87 629-51-08</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+998 87 629-51-08</t>
+          <t>+998 88 183-11-67</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -2727,7 +2755,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob, Iksana MFY, Iskana qishloqi, 40-uy</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -2752,18 +2780,22 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>+998 93 636-79-86</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr"/>
+          <t>+998 87 934-76-08</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>+998 91 456-46-61</t>
+        </is>
+      </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, BektimirMFY, Yoshlar kuchasi, 27-uy</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -2788,18 +2820,22 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>+998 77 818-18-56</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>+998 97 618-02-59</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Beshariq MFY, Mehrobod, 45-uy</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -2839,7 +2875,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Katlos mfy, Obigarm kuchasi, 89.0</t>
+          <t>Kitob tumani, Katlos mfy, Obigarm kuchasi, 89-uy</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -2909,7 +2945,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>+998 99 569-81-12</t>
+          <t>+998 99 568-81-12</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -2919,7 +2955,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Oqsuv MFY, Nimgi qishloq, 152-uy</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -2999,7 +3035,7 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Miraki mfy, Navoiy ko'chasi, 68.0</t>
+          <t>Shahrisabz tumani, Miraki mfy, Navoiy ko'chasi, 68-uy</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -3024,7 +3060,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>+998 70 188-54-32</t>
+          <t>+998 77 838-07-48</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -3034,12 +3070,12 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrissbz tumani, Zangi, Keldihayot koʻchasi 290, 290-uy</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -3067,7 +3103,11 @@
           <t>+998 91 957-18-58</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 034-05-30</t>
+        </is>
+      </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -3075,7 +3115,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tuman, Hamid Olimjon, Zilol buloq, 17-uy</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -3115,7 +3155,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Hamid Olimjon MFY, Amir Temur, 69.0</t>
+          <t>Kitob tumani, Hamid Olimjon MFY, Amir Temur, 69-uy</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -3180,7 +3220,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>+998 91 949-16-27</t>
+          <t>+998 90 069-89-98</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -3195,7 +3235,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shaxresabiz tumani, Quchi MFY, Quchi kuchasi, 56-uy</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -3267,7 +3307,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Sayyod MFY, Obod mahallasi, 13.0</t>
+          <t>Shahrisabz tumani, Sayyod MFY, Obod mahallasi, 13-uy</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -3307,7 +3347,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Surum mahallasi, Sokin koʻchasi, 66.0</t>
+          <t>Kitob tumani, Surum mahallasi, Sokin koʻchasi, 66-uy</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -3372,7 +3412,7 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>+998 90 894-24-71</t>
+          <t>+998 90 864-24-71</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -3382,12 +3422,12 @@
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Dustlik MFY, Bunyodkor kuchasi, 97-uy</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -3467,7 +3507,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Jilisuv MFY, Yangi Jilisuv, 99.0</t>
+          <t>Kitob tumani, Jilisuv MFY, Yangi Jilisuv, 99-uy</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -3647,7 +3687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I40"/>
+  <dimension ref="B2:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="2" max="2"/>
@@ -3670,7 +3710,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Guruh: 26-06 | Talabalar soni: 35 nafar</t>
+          <t>Guruh: 26-06 | Talabalar soni: 34 nafar</t>
         </is>
       </c>
     </row>
@@ -3732,22 +3772,22 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>+998 90 341-06-76</t>
+          <t>+998 91 898-04-95</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>+998 91 898-04-95</t>
+          <t>+998 90 883-08-65</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saray MFY, Yangiqishloq, 81-uy</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -3815,7 +3855,11 @@
           <t>+998 97 799-76-71</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+998 88 403-76-71</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -3823,7 +3867,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shaxar, Kesh mahalas, Kalakon kuchas, 73-uy</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -3933,7 +3977,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>+998 91 949-04-81</t>
+          <t>+998 91 223-75-20</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
@@ -3943,7 +3987,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog‘ tumani, Darxon MFY, Eshonguzar, 52-uy</t>
+          <t>Shahrisabz tumani, Darxon MFY, Eshonguzar kôchasi, 52-uy</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -3966,16 +4010,24 @@
           <t>01.06.2003</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 562-65-77</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 812-70-80</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Opasi / Singlisi</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz Shahar, Farovon, Farovon kuchasi, 14-uy</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -4000,22 +4052,22 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
+          <t>+998 77 810-82-80</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
           <t>+998 91 952-43-44</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>+998 90 442-22-47</t>
-        </is>
-      </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shaxar, Sinabog MFY, oqshom, 112-uy</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -4080,14 +4132,10 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>+998 70 034-95-05</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>+998 99 468-84-06</t>
-        </is>
-      </c>
+          <t>+998 70 034-95-05 / +998 99 468-84-06 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr"/>
       <c r="G15" s="9" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -4130,12 +4178,12 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>O'zi</t>
+          <t>Otasi / Onasi</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Kitob tuman, Katlos MFY, Oshqon kuchasi, 69-uy</t>
+          <t>Kitob tumani, Katlos MFY, Oshqon, 69-uy</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -4211,7 +4259,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Sariosiyo MFY, Chinorlik ko'chasi, 14.0</t>
+          <t>Kitob tumani, Sariosiyo MFY, Chinorlik koʻchasi, 14-uy</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -4241,7 +4289,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>+998 90 617-68-83</t>
+          <t>+998 91 617-68-83</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -4251,7 +4299,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Ulugʻbek MFY, Qizil darvoza kuchasi, 116.0</t>
+          <t>Kitob tumani, Ulugʻbek MFY, Qizil darvoza kuchasi, 116-uy</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -4276,27 +4324,27 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>+998 91 217-14-30</t>
+          <t>+998 88 244-68-08</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>+998 94 134-34-03</t>
+          <t>+998 88 027-15-82</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi, Hamid olimjon MFY, Haytkul, 115-uy</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -4462,16 +4510,24 @@
           <t>12.06.1989</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 386-56-12</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 382-46-06</t>
+        </is>
+      </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Turmush o'rtog'i</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Xujahurason mahalla, Sugʻdiyona, 50-uy</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -4511,7 +4567,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>Kitob  rayon, Oqsuv MFY, Nimgi qishloq, 38_uy</t>
+          <t>Kitob tumani, Oqsuv, Nimgi qishloq, 38-uy</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -4551,7 +4607,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Miraki mahallasi, Navoiy, 84 uy</t>
+          <t>Miraki, Alisher Navoiy, Navoiy kuchasi, 84 uy</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -4591,7 +4647,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Yomchi, Abdulqosim Firdavsiy, 134-uy</t>
+          <t>Shahrisabz tumani, Q9oʻrgʻon tepa MFY, Abdulqodimfirdavsiy koʻchasi, 134-uy</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -4631,7 +4687,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Qamashi, Yuksalish MFY, Olmazor, 124.0</t>
+          <t>Qamashi tumani, Yuksalish MFY, Olmazor koʻchasi, 124-uy</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -4711,7 +4767,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Yashil diyor mfy, Yashil diyor kuchasi, 118.0</t>
+          <t>Shahrisabz shahri, Yashil diyor 116, Yashil diyor kuchasi, 118 uy</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -4751,7 +4807,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Shaxrisabz tumani, Meraki MFY, NAVOIY KÖCHASI, 48.0</t>
+          <t>Shaxrisabz tumani, Meraki MFY, NAVOIY KÖCHASI, 48-uy</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -4774,16 +4830,24 @@
           <t>15.07.1998</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr"/>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>+998 50 589-58-77</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>+998 87 194-72-76</t>
+        </is>
+      </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Boston MFY, Kenagaz, 73- uy</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -4818,17 +4882,17 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkaboğ tumani, Yashnabod MFY, Faravon kochasi, 223-uy</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -4914,22 +4978,22 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>16.04.2006</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>+998 93 891-85-90</t>
+          <t>+998 90 881-06-10</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>+998 97 635-02-69</t>
+          <t>+998 90 863-16-74</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -4939,7 +5003,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Shaxrisabz tumani, Shamaton MFY, Yangiobod1, 111 uy</t>
+          <t>Shahrisabz shahar, Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -4954,22 +5018,22 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>28.02.2008</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>+998 90 881-06-10</t>
+          <t>+998 77 371-00-28</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>+998 90 863-16-74</t>
+          <t>+998 95 665-28-82</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -4979,7 +5043,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
+          <t>Kitob tumani, Oqsuv MFY, Nimgi qishlog'i, 156uy</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -4994,22 +5058,22 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>28.02.2008</t>
+          <t>30.07.2008</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>+998 77 371-00-28</t>
+          <t>+998 87 561-30-02</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>+998 95 665-28-82</t>
+          <t>+998 90 518-18-84</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -5019,50 +5083,10 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Oqsuv MFY, Yoshlar kuchasi, 156-uy</t>
+          <t>Kiuob tumani, Ulubek MFY, Oʻrikzor koʻchasi, 23-uy</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>O'z uyidan</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="B40" s="4" t="n">
-        <v>35</v>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>30.07.2008</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>+998 90 518-18-84</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>+998 87 561-30-02</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>O'z uyidan</t>
         </is>
@@ -5079,7 +5103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F186"/>
+  <dimension ref="B2:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -5396,7 +5420,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>+998 90 878-81-08</t>
+          <t>+998 70 066-73-09</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -5546,7 +5570,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>+998 88 617-78-60</t>
+          <t>+998 97 619-02-15</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -5646,7 +5670,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>+998 97 335-05-82</t>
+          <t>+998 97 863-50-82</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -5696,7 +5720,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>+998 91 217-43-55</t>
+          <t>+998 77 864-19-17</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -5940,7 +5964,11 @@
           <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>+998 95 050-54-08</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -6036,7 +6064,11 @@
           <t>Shonazarova Vazira Botir qizi</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -6109,7 +6141,7 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>+998 88 868-99-08</t>
+          <t>+998 88 336-77-74</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -6430,7 +6462,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>+998 95 259-06-25</t>
+          <t>+998 95 259-06-25 / +998 99 152-33-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -6455,7 +6487,7 @@
       </c>
       <c r="E59" s="9" t="inlineStr">
         <is>
-          <t>+998 87 358-87-97</t>
+          <t>+998 87 358-87-97 / +998 88 632-19-72 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F59" s="9" t="inlineStr">
@@ -6480,7 +6512,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>+998 99 943-05-96</t>
+          <t>+998 95 939-92-05</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -6530,7 +6562,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>+998 88 803-91-93</t>
+          <t>+998 88 803-91-93 / +998 88 726-14-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -6672,7 +6704,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>+998 87 392-00-25</t>
+          <t>+998 87 392-00-25 / +998 87 392-00-21 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6968,7 +7000,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>+998 87 561-52-96</t>
+          <t>+998 87 561-52-96 / +998 77 232-28-78 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -7018,7 +7050,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>+998 88 865-90-08</t>
+          <t>+998 88 981-83-80</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -7143,7 +7175,7 @@
       </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>+998 97 960-25-35</t>
+          <t>+998 97 960-25-35 / +998 91 216-23-04 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F87" s="9" t="inlineStr">
@@ -7193,7 +7225,7 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>+998 93 019-06-86</t>
+          <t>+998 70 331-87-08</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
@@ -7218,7 +7250,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>+998 91 948-38-79</t>
+          <t>+998 87 926-61-08</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -7318,7 +7350,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>+998 99 153-48-38</t>
+          <t>+998 99 153-48-38 / +998 70 034-22-44 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -7368,7 +7400,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>+998 91 005-49-08</t>
+          <t>+998 88 205-49-08</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -7616,7 +7648,11 @@
           <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>+998 93 804-18-14</t>
+        </is>
+      </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -7839,7 +7875,7 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>+998 97 676-09-05</t>
+          <t>+998 97 787-47-95</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
@@ -7964,7 +8000,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>+998 91 871-57-37</t>
+          <t>+998 77 006-91-49</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -8014,7 +8050,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>+998 87 636-07-08</t>
+          <t>+998 87 636-07-08 / +998 97 636-37-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -8114,7 +8150,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>+998 88 100-95-04</t>
+          <t>+998 88 100-95-04 / +998 97 632-55-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -8139,7 +8175,7 @@
       </c>
       <c r="E127" s="9" t="inlineStr">
         <is>
-          <t>+998 77 629-45-08</t>
+          <t>+998 95 740-19-81</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
@@ -8164,7 +8200,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>+998 88 619-97-03</t>
+          <t>+998 87 629-51-08</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -8189,7 +8225,7 @@
       </c>
       <c r="E129" s="9" t="inlineStr">
         <is>
-          <t>+998 93 636-79-86</t>
+          <t>+998 87 934-76-08</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
@@ -8214,7 +8250,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>+998 97 618-02-59</t>
+          <t>+998 77 818-18-56</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -8364,7 +8400,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>+998 70 188-54-32</t>
+          <t>+998 77 838-07-48</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -8464,7 +8500,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>+998 91 949-16-27</t>
+          <t>+998 90 069-89-98</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -8585,7 +8621,7 @@
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>+998 90 894-24-71</t>
+          <t>+998 90 864-24-71</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
@@ -8760,7 +8796,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>+998 90 341-06-76</t>
+          <t>+998 91 898-04-95</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -8908,7 +8944,11 @@
           <t>Irgasheva Dinora Shodmon qizi</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 562-65-77</t>
+        </is>
+      </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -8931,7 +8971,7 @@
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>+998 91 952-43-44</t>
+          <t>+998 77 810-82-80</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
@@ -8981,7 +9021,7 @@
       </c>
       <c r="E161" s="9" t="inlineStr">
         <is>
-          <t>+998 70 034-95-05</t>
+          <t>+998 70 034-95-05 / +998 99 468-84-06 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="F161" s="9" t="inlineStr">
@@ -9106,7 +9146,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>+998 91 217-14-30</t>
+          <t>+998 88 244-68-08</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -9225,7 +9265,11 @@
           <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr"/>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 386-56-12</t>
+        </is>
+      </c>
       <c r="F171" s="9" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -9421,7 +9465,11 @@
           <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
-      <c r="E179" s="9" t="inlineStr"/>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>+998 50 589-58-77</t>
+        </is>
+      </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -9514,12 +9562,12 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
         <is>
-          <t>+998 93 891-85-90</t>
+          <t>+998 90 881-06-10</t>
         </is>
       </c>
       <c r="F183" s="9" t="inlineStr">
@@ -9539,12 +9587,12 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>+998 90 881-06-10</t>
+          <t>+998 77 371-00-28</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -9564,40 +9612,15 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
         <is>
-          <t>+998 77 371-00-28</t>
+          <t>+998 87 561-30-02</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>T-40/2 02.09.2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="B186" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>+998 90 518-18-84</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
         </is>
@@ -9614,7 +9637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F186"/>
+  <dimension ref="B2:F185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -9931,7 +9954,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boston MFY, Abdulla Qodiriy köchasi, 31-uy</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -9956,7 +9979,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Duxchi MFY, Duxchi qishlog'i, 148.0</t>
+          <t>Shahrisabz tumani, Duxchi MFY, Duxchi qishlog'i, 148-uy</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -9981,7 +10004,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Dòstlik MFY, Dòstlik kuchasi, 19-uy</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -10006,7 +10029,7 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Sinabog' M F Y, Sinabog' mahallasi, 101-uy</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
@@ -10031,7 +10054,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guluston, Guluston, 4.0</t>
+          <t>Kitob tumani, Guluston, Guluston, 4-uy</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -10056,7 +10079,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Kesh MFY, Kalakon kucha, 91-uy</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -10081,7 +10104,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Pakkandi MFY, Safarabot, 29_uy</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -10181,7 +10204,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Yangiqishloq, 44-uy</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -10231,7 +10254,7 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Turon MFY, Yangi obod, 62-uy</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -10256,7 +10279,7 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Saroy koʻchasi, 17-uy</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -10281,7 +10304,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kotob tumani, Sevaz MFY, Taraqqiyot kuchasi, 130-uy</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -10306,7 +10329,7 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44.0</t>
+          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44-uy</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -10331,7 +10354,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35.0</t>
+          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35-uy</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -10481,7 +10504,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Qamashi, Yuksalish MFY, Olmazor, 183-uy</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -10581,7 +10604,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Qashqadaryo MFY, Minjir qishlogʻi, 51-uy</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -10606,7 +10629,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz Shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
+          <t>Shahrisabz shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -10631,7 +10654,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432.0</t>
+          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432-uy</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -10656,7 +10679,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Shanbe MFY, Shabboda, 35 -uy</t>
+          <t>Shahrisabz shahar, Do'stlik MFY, Bunyodkor ko'chasi, 62/16-uy</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
@@ -10681,7 +10704,7 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boģbon MFY, Ochamayli kòchasi, 100-uy</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -10781,7 +10804,7 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84.0</t>
+          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84-uy</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -10856,7 +10879,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Ayoqchi MFY, Qovchin qishlogʻi, 92uy</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
@@ -10931,7 +10954,7 @@
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabogʻ tumani, Tatar MFY, Yangi hayot koʻchasi, 49_uy</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -11031,7 +11054,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Gelon MFY, Gelon, 43uy</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -11206,7 +11229,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Oq Oltin MFY, Al- Xorazmiy, 212.0</t>
+          <t>Shahrisabz tumani, Oq Oltin MFY, Al- Xorazmiy, 212-uy</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
@@ -11256,7 +11279,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Shahrizabz tumani, Turon MFY, Turon koʻchasi, 52.0</t>
+          <t>Shahrizabz tumani, Turon MFY, Turon koʻchasi, 52-uy</t>
         </is>
       </c>
       <c r="F69" s="9" t="inlineStr">
@@ -11356,7 +11379,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Bunyodkor, Alpomish, 13-uy</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
@@ -11406,7 +11429,7 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Yakkabogʼ, Chagʼatoy, Yuq, 76.0</t>
+          <t>Yakkabogʼ, Chagʼatoy, Yuq, 76-uy</t>
         </is>
       </c>
       <c r="F75" s="9" t="inlineStr">
@@ -11431,7 +11454,7 @@
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabiz tumani, Sanam MFY, Uzumzor kochasi, 60.0</t>
+          <t>Shahrisabiz tumani, Sanam MFY, Uzumzor kochasi, 60-uy</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -11506,7 +11529,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Китабский район, Рус кишлак МФЮ, Улица Рус кишлак, Дом-11</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
@@ -11556,7 +11579,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>китоб, китоб МФЯ, гулустон кучаси, 90.0</t>
+          <t>китоб, китоб МФЯ, гулустон кучаси, 90-uy</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
@@ -11581,7 +11604,7 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Bogʻishamol MFY, Qorapoycha, 6 uy</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -11656,7 +11679,7 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog', Kenguzar MFY, Chig'atoy, 6.0</t>
+          <t>Yakkabog', Kenguzar MFY, Chig'atoy, 6-uy</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
@@ -11681,7 +11704,7 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Xoji MFY, Uzunqir kuchasi, 106.0</t>
+          <t>Kitob tumani, Xoji MFY, Uzunqir kuchasi, 106-uy</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -11731,7 +11754,7 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Kichik novqat mfy, Soyboʻyi koʻchasi, 04</t>
+          <t>Shahrisabz tumani, Maktobod mfy, Soyboʻyi koʻchasi, 4-uy</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -11756,7 +11779,7 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Quruqsoy MFY, Buzovut qishlogʻi, 111-uy</t>
         </is>
       </c>
       <c r="F89" s="9" t="inlineStr">
@@ -11781,7 +11804,7 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Nomozgoh MFY, Taragʻay Bahodir, 2.31-uy</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -11856,7 +11879,7 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Yakkabogʻ tumani, Alakuylak MFY, Hamid Olimjon koʻchasi, 55.0</t>
+          <t>Yakkabogʻ tumani, Alakuylak MFY, Hamid Olimjon koʻchasi, 55-uy</t>
         </is>
       </c>
       <c r="F93" s="9" t="inlineStr">
@@ -11931,7 +11954,7 @@
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Katlos MFY, Bogʻiston kòchasi, 28-uy</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -11956,7 +11979,7 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, Guliston  MFY, Qoʻshtepa kòchasi, 329.0</t>
+          <t>Shahrisabz shahar, Guliston MFY, Qoʻshtepa kòchasi, 329-uy</t>
         </is>
       </c>
       <c r="F97" s="9" t="inlineStr">
@@ -12031,7 +12054,7 @@
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Iskana MFY, Uchtepalik, 52.0</t>
+          <t>Kitob tumani, Iskana MFY, Uchtepalik, 52-uy</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -12131,7 +12154,7 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49.0</t>
+          <t>Kitob tumani, Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49-uy</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -12181,7 +12204,7 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Abziyat MFY, Hidoyat ko’chasi, 1-uy</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -12206,7 +12229,7 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Xitoy MFY, Besh chinor, 65.0</t>
+          <t>Shahrisabz tuman, Xitoy MFY, Besh chinor, 65-uy</t>
         </is>
       </c>
       <c r="F107" s="9" t="inlineStr">
@@ -12281,7 +12304,7 @@
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guliston MFY, Qo'shtepa mahallasi, 75.0</t>
+          <t>Kitob tumani, Guliston MFY, Qo'shtepa mahallasi, 75-uy</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -12406,7 +12429,7 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Chiroqchi MFY, Elabot kuchasi, 227-uy</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
@@ -12456,7 +12479,7 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Xalqlar do'stligi MFY, Qashqadaryo2, 65.0</t>
+          <t>Kitob tumani, Xalqlar do'stligi MFY, Qashqadaryo2, 65-uy</t>
         </is>
       </c>
       <c r="F117" s="9" t="inlineStr">
@@ -12481,7 +12504,7 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Qumqishloq MFY, Hoji koʻchasi, 2-uy</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -12531,7 +12554,7 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Taragʻay MFY, Taragʻay, Yuq</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -12706,7 +12729,7 @@
       </c>
       <c r="E127" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Toʻdamaydon, Fidokor, 92.0</t>
+          <t>Shahrisabz tumani, Toʻdamaydon, Fidokor, 92-uy</t>
         </is>
       </c>
       <c r="F127" s="9" t="inlineStr">
@@ -12731,7 +12754,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob, Iksana MFY, Iskana qishloqi, 40-uy</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -12756,7 +12779,7 @@
       </c>
       <c r="E129" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, BektimirMFY, Yoshlar kuchasi, 27-uy</t>
         </is>
       </c>
       <c r="F129" s="9" t="inlineStr">
@@ -12781,7 +12804,7 @@
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Beshariq MFY, Mehrobod, 45-uy</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -12806,7 +12829,7 @@
       </c>
       <c r="E131" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Katlos mfy, Obigarm kuchasi, 89.0</t>
+          <t>Kitob tumani, Katlos mfy, Obigarm kuchasi, 89-uy</t>
         </is>
       </c>
       <c r="F131" s="9" t="inlineStr">
@@ -12856,7 +12879,7 @@
       </c>
       <c r="E133" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Oqsuv MFY, Nimgi qishloq, 152-uy</t>
         </is>
       </c>
       <c r="F133" s="9" t="inlineStr">
@@ -12906,7 +12929,7 @@
       </c>
       <c r="E135" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Miraki mfy, Navoiy ko'chasi, 68.0</t>
+          <t>Shahrisabz tumani, Miraki mfy, Navoiy ko'chasi, 68-uy</t>
         </is>
       </c>
       <c r="F135" s="9" t="inlineStr">
@@ -12931,7 +12954,7 @@
       </c>
       <c r="E136" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrissbz tumani, Zangi, Keldihayot koʻchasi 290, 290-uy</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -12956,7 +12979,7 @@
       </c>
       <c r="E137" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tuman, Hamid Olimjon, Zilol buloq, 17-uy</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
@@ -12981,7 +13004,7 @@
       </c>
       <c r="E138" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Hamid Olimjon MFY, Amir Temur, 69.0</t>
+          <t>Kitob tumani, Hamid Olimjon MFY, Amir Temur, 69-uy</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -13031,7 +13054,7 @@
       </c>
       <c r="E140" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shaxresabiz tumani, Quchi MFY, Quchi kuchasi, 56-uy</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -13081,7 +13104,7 @@
       </c>
       <c r="E142" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Sayyod MFY, Obod mahallasi, 13.0</t>
+          <t>Shahrisabz tumani, Sayyod MFY, Obod mahallasi, 13-uy</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -13106,7 +13129,7 @@
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Surum mahallasi, Sokin koʻchasi, 66.0</t>
+          <t>Kitob tumani, Surum mahallasi, Sokin koʻchasi, 66-uy</t>
         </is>
       </c>
       <c r="F143" s="9" t="inlineStr">
@@ -13156,7 +13179,7 @@
       </c>
       <c r="E145" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Dustlik MFY, Bunyodkor kuchasi, 97-uy</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
@@ -13206,7 +13229,7 @@
       </c>
       <c r="E147" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Jilisuv MFY, Yangi Jilisuv, 99.0</t>
+          <t>Kitob tumani, Jilisuv MFY, Yangi Jilisuv, 99-uy</t>
         </is>
       </c>
       <c r="F147" s="9" t="inlineStr">
@@ -13331,7 +13354,7 @@
       </c>
       <c r="E152" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saray MFY, Yangiqishloq, 81-uy</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -13381,7 +13404,7 @@
       </c>
       <c r="E154" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shaxar, Kesh mahalas, Kalakon kuchas, 73-uy</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -13456,7 +13479,7 @@
       </c>
       <c r="E157" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog‘ tumani, Darxon MFY, Eshonguzar, 52-uy</t>
+          <t>Shahrisabz tumani, Darxon MFY, Eshonguzar kôchasi, 52-uy</t>
         </is>
       </c>
       <c r="F157" s="9" t="inlineStr">
@@ -13481,7 +13504,7 @@
       </c>
       <c r="E158" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz Shahar, Farovon, Farovon kuchasi, 14-uy</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -13506,7 +13529,7 @@
       </c>
       <c r="E159" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shaxar, Sinabog MFY, oqshom, 112-uy</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
@@ -13581,7 +13604,7 @@
       </c>
       <c r="E162" s="7" t="inlineStr">
         <is>
-          <t>Kitob tuman, Katlos MFY, Oshqon kuchasi, 69-uy</t>
+          <t>Kitob tumani, Katlos MFY, Oshqon, 69-uy</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -13631,7 +13654,7 @@
       </c>
       <c r="E164" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Sariosiyo MFY, Chinorlik ko'chasi, 14.0</t>
+          <t>Kitob tumani, Sariosiyo MFY, Chinorlik koʻchasi, 14-uy</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -13656,7 +13679,7 @@
       </c>
       <c r="E165" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Ulugʻbek MFY, Qizil darvoza kuchasi, 116.0</t>
+          <t>Kitob tumani, Ulugʻbek MFY, Qizil darvoza kuchasi, 116-uy</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
@@ -13681,7 +13704,7 @@
       </c>
       <c r="E166" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi, Hamid olimjon MFY, Haytkul, 115-uy</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -13806,7 +13829,7 @@
       </c>
       <c r="E171" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Xujahurason mahalla, Sugʻdiyona, 50-uy</t>
         </is>
       </c>
       <c r="F171" s="9" t="inlineStr">
@@ -13831,7 +13854,7 @@
       </c>
       <c r="E172" s="7" t="inlineStr">
         <is>
-          <t>Kitob  rayon, Oqsuv MFY, Nimgi qishloq, 38_uy</t>
+          <t>Kitob tumani, Oqsuv, Nimgi qishloq, 38-uy</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -13856,7 +13879,7 @@
       </c>
       <c r="E173" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Miraki mahallasi, Navoiy, 84 uy</t>
+          <t>Miraki, Alisher Navoiy, Navoiy kuchasi, 84 uy</t>
         </is>
       </c>
       <c r="F173" s="9" t="inlineStr">
@@ -13881,7 +13904,7 @@
       </c>
       <c r="E174" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Yomchi, Abdulqosim Firdavsiy, 134-uy</t>
+          <t>Shahrisabz tumani, Q9oʻrgʻon tepa MFY, Abdulqodimfirdavsiy koʻchasi, 134-uy</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -13906,7 +13929,7 @@
       </c>
       <c r="E175" s="12" t="inlineStr">
         <is>
-          <t>Qamashi, Yuksalish MFY, Olmazor, 124.0</t>
+          <t>Qamashi tumani, Yuksalish MFY, Olmazor koʻchasi, 124-uy</t>
         </is>
       </c>
       <c r="F175" s="9" t="inlineStr">
@@ -13956,7 +13979,7 @@
       </c>
       <c r="E177" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Yashil diyor mfy, Yashil diyor kuchasi, 118.0</t>
+          <t>Shahrisabz shahri, Yashil diyor 116, Yashil diyor kuchasi, 118 uy</t>
         </is>
       </c>
       <c r="F177" s="9" t="inlineStr">
@@ -13981,7 +14004,7 @@
       </c>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>Shaxrisabz tumani, Meraki MFY, NAVOIY KÖCHASI, 48.0</t>
+          <t>Shaxrisabz tumani, Meraki MFY, NAVOIY KÖCHASI, 48-uy</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -14006,7 +14029,7 @@
       </c>
       <c r="E179" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Boston MFY, Kenagaz, 73- uy</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
@@ -14031,7 +14054,7 @@
       </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkaboğ tumani, Yashnabod MFY, Faravon kochasi, 223-uy</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -14101,17 +14124,17 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr">
         <is>
-          <t>Shaxrisabz tumani, Shamaton MFY, Yangiobod1, 111 uy</t>
+          <t>Shahrisabz shahar, Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
         </is>
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>07.12.1990</t>
+          <t>16.04.2006</t>
         </is>
       </c>
     </row>
@@ -14126,17 +14149,17 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
+          <t>Kitob tumani, Oqsuv MFY, Nimgi qishlog'i, 156uy</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>16.04.2006</t>
+          <t>28.02.2008</t>
         </is>
       </c>
     </row>
@@ -14151,40 +14174,15 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Oqsuv MFY, Yoshlar kuchasi, 156-uy</t>
+          <t>Kiuob tumani, Ulubek MFY, Oʻrikzor koʻchasi, 23-uy</t>
         </is>
       </c>
       <c r="F185" s="9" t="inlineStr">
-        <is>
-          <t>28.02.2008</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="B186" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
         <is>
           <t>30.07.2008</t>
         </is>
@@ -14201,7 +14199,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G186"/>
+  <dimension ref="B2:G185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -14532,8 +14530,16 @@
           <t>Ravshanova Ruhshona Radju qizi</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+998 70 390-23-08</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
@@ -14578,7 +14584,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -14602,8 +14608,16 @@
           <t>Ziyodullayeva Jasmina Alisher qizi</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>Otasi</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>+998 91 224-00-18</t>
+        </is>
+      </c>
       <c r="G19" s="9" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
@@ -14646,8 +14660,16 @@
           <t>Berdiqulova Gulshan Rustam qizi</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>Opasi / Singlisi</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 319-62-60</t>
+        </is>
+      </c>
       <c r="G21" s="9" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -14666,12 +14688,12 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>+998 91 457-78-60</t>
+          <t>+998 88 731-19-69</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
@@ -14770,12 +14792,12 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Ukasi</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>+998 97 863-50-82</t>
+          <t>+998 97 355-05-82</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
@@ -14820,8 +14842,16 @@
           <t>Islomova Nilufar Abdulxafiz qizi</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 217-43-55</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="20" customHeight="1">
@@ -14840,12 +14870,12 @@
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
         <is>
-          <t>+998 91 815-13-09</t>
+          <t>+998 91 817-20-73</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr"/>
@@ -14864,8 +14894,16 @@
           <t>Javliyeva Nargiza Ortiq qizi</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 561-30-02</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="20" customHeight="1">
@@ -15048,8 +15086,16 @@
           <t>Ro'zimurodova Larisa Ma'matali qizi</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>+998 99 062-62-08</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -15136,8 +15182,16 @@
           <t>Shonazarova Vazira Botir qizi</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Otasi / Onasi</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -15208,12 +15262,12 @@
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F45" s="9" t="inlineStr">
         <is>
-          <t>+998 95 770-11-69</t>
+          <t>+998 90 716-31-42</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr"/>
@@ -15232,8 +15286,16 @@
           <t>To'xtayeva Durdona Nazim qizi</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Otasi / Onasi</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>+998 87 465-05-87</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr"/>
     </row>
     <row r="47" ht="20" customHeight="1">
@@ -15408,12 +15470,12 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>+998 88 977-06-93</t>
+          <t>+998 99 201-92-74</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr"/>
@@ -15476,8 +15538,16 @@
           <t>Eshnazarova Dilnoza Rustam qizi</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr"/>
-      <c r="F56" s="4" t="inlineStr"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 812-76-97</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57" ht="20" customHeight="1">
@@ -15520,16 +15590,8 @@
           <t>Ibragimova Gulnoza Isroil qizi</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>+998 99 152-33-71</t>
-        </is>
-      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr"/>
     </row>
     <row r="59" ht="20" customHeight="1">
@@ -15546,16 +15608,8 @@
           <t>Izzatulloyeva Vazira G'ayratzoda</t>
         </is>
       </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>+998 88 632-19-72</t>
-        </is>
-      </c>
+      <c r="E59" s="9" t="inlineStr"/>
+      <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
     </row>
     <row r="60" ht="20" customHeight="1">
@@ -15574,12 +15628,12 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>+998 95 939-92-05</t>
+          <t>+998 95 233-27-66</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
@@ -15624,16 +15678,8 @@
           <t>Murtazayeva Kamola Jamoliddin qizi</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>+998 88 726-14-12</t>
-        </is>
-      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr"/>
     </row>
     <row r="63" ht="20" customHeight="1">
@@ -15764,16 +15810,8 @@
           <t>Primova Husnora Shovkat qizi</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>+998 87 392-00-21</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="4" t="inlineStr"/>
       <c r="G68" s="4" t="inlineStr"/>
     </row>
     <row r="69" ht="20" customHeight="1">
@@ -15888,7 +15926,7 @@
       </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="F73" s="9" t="inlineStr">
@@ -16042,8 +16080,16 @@
           <t>Tursunmurodova Diyora Jasur qizi</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 389-82-04</t>
+        </is>
+      </c>
       <c r="G79" s="9" t="inlineStr"/>
     </row>
     <row r="80" ht="20" customHeight="1">
@@ -16060,16 +16106,8 @@
           <t>Umirova Sevinch Avlayor qizi</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>+998 77 232-28-78</t>
-        </is>
-      </c>
+      <c r="E80" s="4" t="inlineStr"/>
+      <c r="F80" s="4" t="inlineStr"/>
       <c r="G80" s="4" t="inlineStr"/>
     </row>
     <row r="81" ht="20" customHeight="1">
@@ -16114,12 +16152,12 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>+998 88 186-17-12</t>
+          <t>+998 88 386-17-12</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
@@ -16242,16 +16280,8 @@
           <t>Xurramova Sabina Yuldosh qizi</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F87" s="9" t="inlineStr">
-        <is>
-          <t>+998 91 216-23-04</t>
-        </is>
-      </c>
+      <c r="E87" s="9" t="inlineStr"/>
+      <c r="F87" s="9" t="inlineStr"/>
       <c r="G87" s="9" t="inlineStr"/>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -16275,7 +16305,7 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>+998 87 607-82-87</t>
+          <t>+998 88 607-82-87</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
@@ -16294,8 +16324,16 @@
           <t>Abdixalilova Shohzoda Bahodir qizi</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr"/>
-      <c r="F89" s="9" t="inlineStr"/>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>Otasi / Onasi</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>+998 70 119-06-86</t>
+        </is>
+      </c>
       <c r="G89" s="9" t="inlineStr"/>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -16314,12 +16352,12 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>+998 88 596-71-79</t>
+          <t>+998 91 948-38-79</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr"/>
@@ -16416,16 +16454,8 @@
           <t>G'aniyeva Asila G'ani qizi</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F94" s="4" t="inlineStr">
-        <is>
-          <t>+998 70 034-22-44</t>
-        </is>
-      </c>
+      <c r="E94" s="4" t="inlineStr"/>
+      <c r="F94" s="4" t="inlineStr"/>
       <c r="G94" s="4" t="inlineStr"/>
     </row>
     <row r="95" ht="20" customHeight="1">
@@ -16470,12 +16500,12 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Turmush o'rtog'i</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>+998 93 553-33-51</t>
+          <t>+998 88 753-33-51</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
@@ -16728,8 +16758,16 @@
           <t>Soyipova Dinora Sanjar qizi</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr"/>
-      <c r="F106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>+998 97 385-83-69</t>
+        </is>
+      </c>
       <c r="G106" s="4" t="inlineStr"/>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -16948,12 +16986,12 @@
       </c>
       <c r="E115" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F115" s="9" t="inlineStr">
         <is>
-          <t>+998 87 631-73-71</t>
+          <t>+998 97 697-95-92</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr"/>
@@ -17026,12 +17064,12 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>+998 97 619-84-84</t>
+          <t>+998 97 387-87-37</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
@@ -17076,8 +17114,16 @@
           <t>Abdishukurova Gulsevar Xusniddin qizi</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr"/>
-      <c r="F120" s="4" t="inlineStr"/>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Otasi</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>+998 90 960-45-80</t>
+        </is>
+      </c>
       <c r="G120" s="4" t="inlineStr"/>
     </row>
     <row r="121" ht="20" customHeight="1">
@@ -17120,16 +17166,8 @@
           <t>Ashirova Gulsanam Abduvali qizi</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F122" s="4" t="inlineStr">
-        <is>
-          <t>+998 97 636-37-74</t>
-        </is>
-      </c>
+      <c r="E122" s="4" t="inlineStr"/>
+      <c r="F122" s="4" t="inlineStr"/>
       <c r="G122" s="4" t="inlineStr"/>
     </row>
     <row r="123" ht="20" customHeight="1">
@@ -17224,16 +17262,8 @@
           <t>Eshboboyeva Fotima Nurali qizi</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F126" s="4" t="inlineStr">
-        <is>
-          <t>+998 97 632-55-74</t>
-        </is>
-      </c>
+      <c r="E126" s="4" t="inlineStr"/>
+      <c r="F126" s="4" t="inlineStr"/>
       <c r="G126" s="4" t="inlineStr"/>
     </row>
     <row r="127" ht="20" customHeight="1">
@@ -17257,7 +17287,7 @@
       </c>
       <c r="F127" s="9" t="inlineStr">
         <is>
-          <t>+998 88 738-19-82</t>
+          <t>+998 95 740-19-81</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr"/>
@@ -17283,7 +17313,7 @@
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>+998 87 629-51-08</t>
+          <t>+998 88 183-11-67</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
@@ -17302,8 +17332,16 @@
           <t>Jabborova Bahoroy Shukurullo qizi</t>
         </is>
       </c>
-      <c r="E129" s="9" t="inlineStr"/>
-      <c r="F129" s="9" t="inlineStr"/>
+      <c r="E129" s="9" t="inlineStr">
+        <is>
+          <t>Otasi</t>
+        </is>
+      </c>
+      <c r="F129" s="9" t="inlineStr">
+        <is>
+          <t>+998 91 456-46-61</t>
+        </is>
+      </c>
       <c r="G129" s="9" t="inlineStr"/>
     </row>
     <row r="130" ht="20" customHeight="1">
@@ -17320,8 +17358,16 @@
           <t>Jalilova Jasmina Jamshid qizi</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr"/>
-      <c r="F130" s="4" t="inlineStr"/>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>+998 97 618-02-59</t>
+        </is>
+      </c>
       <c r="G130" s="4" t="inlineStr"/>
     </row>
     <row r="131" ht="20" customHeight="1">
@@ -17397,7 +17443,7 @@
       </c>
       <c r="F133" s="9" t="inlineStr">
         <is>
-          <t>+998 99 569-81-12</t>
+          <t>+998 99 568-81-12</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr"/>
@@ -17470,7 +17516,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -17494,8 +17540,16 @@
           <t>Nazarova Munisa Erkin qizi</t>
         </is>
       </c>
-      <c r="E137" s="9" t="inlineStr"/>
-      <c r="F137" s="9" t="inlineStr"/>
+      <c r="E137" s="9" t="inlineStr">
+        <is>
+          <t>Otasi / Onasi</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 034-05-30</t>
+        </is>
+      </c>
       <c r="G137" s="9" t="inlineStr"/>
     </row>
     <row r="138" ht="20" customHeight="1">
@@ -17688,7 +17742,7 @@
       </c>
       <c r="E145" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F145" s="9" t="inlineStr">
@@ -17870,12 +17924,12 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>+998 91 898-04-95</t>
+          <t>+998 90 883-08-65</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
@@ -17920,8 +17974,16 @@
           <t>Azimova Zahroxon Abdirauf qizi</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr"/>
-      <c r="F154" s="4" t="inlineStr"/>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>Otasi / Onasi</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
+        <is>
+          <t>+998 88 403-76-71</t>
+        </is>
+      </c>
       <c r="G154" s="4" t="inlineStr"/>
     </row>
     <row r="155" ht="20" customHeight="1">
@@ -17997,7 +18059,7 @@
       </c>
       <c r="F157" s="9" t="inlineStr">
         <is>
-          <t>+998 91 949-04-81</t>
+          <t>+998 91 223-75-20</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr"/>
@@ -18016,8 +18078,16 @@
           <t>Irgasheva Dinora Shodmon qizi</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr"/>
-      <c r="F158" s="4" t="inlineStr"/>
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>Opasi / Singlisi</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 812-70-80</t>
+        </is>
+      </c>
       <c r="G158" s="4" t="inlineStr"/>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -18036,12 +18106,12 @@
       </c>
       <c r="E159" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F159" s="9" t="inlineStr">
         <is>
-          <t>+998 90 442-22-47</t>
+          <t>+998 91 952-43-44</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr"/>
@@ -18086,16 +18156,8 @@
           <t>Karimova Nozliya Rustamovna</t>
         </is>
       </c>
-      <c r="E161" s="9" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F161" s="9" t="inlineStr">
-        <is>
-          <t>+998 99 468-84-06</t>
-        </is>
-      </c>
+      <c r="E161" s="9" t="inlineStr"/>
+      <c r="F161" s="9" t="inlineStr"/>
       <c r="G161" s="9" t="inlineStr"/>
     </row>
     <row r="162" ht="20" customHeight="1">
@@ -18114,7 +18176,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>O'zi</t>
+          <t>Otasi / Onasi</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -18189,7 +18251,7 @@
       </c>
       <c r="F165" s="9" t="inlineStr">
         <is>
-          <t>+998 90 617-68-83</t>
+          <t>+998 91 617-68-83</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr"/>
@@ -18210,12 +18272,12 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>+998 94 134-34-03</t>
+          <t>+998 88 027-15-82</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
@@ -18322,8 +18384,16 @@
           <t>Niyozova Sevara Turoqulovna</t>
         </is>
       </c>
-      <c r="E171" s="9" t="inlineStr"/>
-      <c r="F171" s="9" t="inlineStr"/>
+      <c r="E171" s="9" t="inlineStr">
+        <is>
+          <t>Turmush o'rtog'i</t>
+        </is>
+      </c>
+      <c r="F171" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 382-46-06</t>
+        </is>
+      </c>
       <c r="G171" s="9" t="inlineStr"/>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -18522,8 +18592,16 @@
           <t>Sayfieva Sarvinoz Zafar qizi</t>
         </is>
       </c>
-      <c r="E179" s="9" t="inlineStr"/>
-      <c r="F179" s="9" t="inlineStr"/>
+      <c r="E179" s="9" t="inlineStr">
+        <is>
+          <t>Onasi</t>
+        </is>
+      </c>
+      <c r="F179" s="9" t="inlineStr">
+        <is>
+          <t>+998 87 194-72-76</t>
+        </is>
+      </c>
       <c r="G179" s="9" t="inlineStr"/>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -18542,7 +18620,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -18607,7 +18685,7 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
@@ -18617,7 +18695,7 @@
       </c>
       <c r="F183" s="9" t="inlineStr">
         <is>
-          <t>+998 97 635-02-69</t>
+          <t>+998 90 863-16-74</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr"/>
@@ -18633,7 +18711,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -18643,7 +18721,7 @@
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>+998 90 863-16-74</t>
+          <t>+998 95 665-28-82</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
@@ -18659,7 +18737,7 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -18669,36 +18747,10 @@
       </c>
       <c r="F185" s="9" t="inlineStr">
         <is>
-          <t>+998 95 665-28-82</t>
+          <t>+998 90 518-18-84</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr"/>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="B186" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>Otasi / Onasi</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>+998 87 561-30-02</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18711,7 +18763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H186"/>
+  <dimension ref="B2:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="2" max="2"/>
@@ -19105,12 +19157,12 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boston MFY, Abdulla Qodiriy köchasi, 31-uy</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>+998 90 878-81-08</t>
+          <t>+998 70 066-73-09</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr"/>
@@ -19136,7 +19188,7 @@
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Duxchi MFY, Duxchi qishlog'i, 148.0</t>
+          <t>Shahrisabz tumani, Duxchi MFY, Duxchi qishlog'i, 148-uy</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">
@@ -19167,7 +19219,7 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Dòstlik MFY, Dòstlik kuchasi, 19-uy</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -19198,7 +19250,7 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Sinabog' M F Y, Sinabog' mahallasi, 101-uy</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr">
@@ -19229,7 +19281,7 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guluston, Guluston, 4.0</t>
+          <t>Kitob tumani, Guluston, Guluston, 4-uy</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -19260,7 +19312,7 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Kesh MFY, Kalakon kucha, 91-uy</t>
         </is>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -19286,17 +19338,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Pakkandi MFY, Safarabot, 29_uy</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>+998 88 617-78-60</t>
+          <t>+998 97 619-02-15</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr"/>
@@ -19415,12 +19467,12 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Yangiqishloq, 44-uy</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>+998 97 335-05-82</t>
+          <t>+998 97 863-50-82</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr"/>
@@ -19477,12 +19529,12 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Turon MFY, Yangi obod, 62-uy</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>+998 91 217-43-55</t>
+          <t>+998 77 864-19-17</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
@@ -19508,7 +19560,7 @@
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Saroy koʻchasi, 17-uy</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr">
@@ -19539,7 +19591,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kotob tumani, Sevaz MFY, Taraqqiyot kuchasi, 130-uy</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -19570,7 +19622,7 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44.0</t>
+          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44-uy</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
@@ -19601,7 +19653,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35.0</t>
+          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35-uy</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -19778,15 +19830,19 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr"/>
+          <t>Qamashi, Yuksalish MFY, Olmazor, 183-uy</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>+998 95 050-54-08</t>
+        </is>
+      </c>
       <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39" ht="20" customHeight="1">
@@ -19903,10 +19959,14 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr"/>
+          <t>Kitob tumani, Qashqadaryo MFY, Minjir qishlogʻi, 51-uy</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
       <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="20" customHeight="1">
@@ -19930,7 +19990,7 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz Shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
+          <t>Shahrisabz shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -19961,7 +20021,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432.0</t>
+          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432-uy</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -19992,12 +20052,12 @@
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Shanbe MFY, Shabboda, 35 -uy</t>
+          <t>Shahrisabz shahar, Do'stlik MFY, Bunyodkor ko'chasi, 62/16-uy</t>
         </is>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
-          <t>+998 88 868-99-08</t>
+          <t>+998 88 336-77-74</t>
         </is>
       </c>
       <c r="H45" s="9" t="inlineStr"/>
@@ -20023,7 +20083,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boģbon MFY, Ochamayli kòchasi, 100-uy</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -20147,7 +20207,7 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84.0</t>
+          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84-uy</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -20235,12 +20295,12 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Ayoqchi MFY, Qovchin qishlogʻi, 92uy</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
@@ -20324,12 +20384,12 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabogʻ tumani, Tatar MFY, Yangi hayot koʻchasi, 49_uy</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -20396,7 +20456,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>+998 95 259-06-25</t>
+          <t>+998 95 259-06-25 / +998 99 152-33-71 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr"/>
@@ -20427,7 +20487,7 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>+998 87 358-87-97</t>
+          <t>+998 87 358-87-97 / +998 88 632-19-72 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr"/>
@@ -20453,12 +20513,12 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Gelon MFY, Gelon, 43uy</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>+998 99 943-05-96</t>
+          <t>+998 95 939-92-05</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr"/>
@@ -20520,7 +20580,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>+998 88 803-91-93</t>
+          <t>+998 88 803-91-93 / +998 88 726-14-12 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr"/>
@@ -20662,7 +20722,7 @@
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Oq Oltin MFY, Al- Xorazmiy, 212.0</t>
+          <t>Shahrisabz tumani, Oq Oltin MFY, Al- Xorazmiy, 212-uy</t>
         </is>
       </c>
       <c r="G67" s="9" t="inlineStr">
@@ -20698,7 +20758,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>+998 87 392-00-25</t>
+          <t>+998 87 392-00-25 / +998 87 392-00-21 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr"/>
@@ -20724,7 +20784,7 @@
       </c>
       <c r="F69" s="12" t="inlineStr">
         <is>
-          <t>Shahrizabz tumani, Turon MFY, Turon koʻchasi, 52.0</t>
+          <t>Shahrizabz tumani, Turon MFY, Turon koʻchasi, 52-uy</t>
         </is>
       </c>
       <c r="G69" s="9" t="inlineStr">
@@ -20844,7 +20904,7 @@
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Bunyodkor, Alpomish, 13-uy</t>
         </is>
       </c>
       <c r="G73" s="9" t="inlineStr">
@@ -20906,7 +20966,7 @@
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Yakkabogʼ, Chagʼatoy, Yuq, 76.0</t>
+          <t>Yakkabogʼ, Chagʼatoy, Yuq, 76-uy</t>
         </is>
       </c>
       <c r="G75" s="9" t="inlineStr">
@@ -20937,7 +20997,7 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabiz tumani, Sanam MFY, Uzumzor kochasi, 60.0</t>
+          <t>Shahrisabiz tumani, Sanam MFY, Uzumzor kochasi, 60-uy</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -21030,7 +21090,7 @@
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Китабский район, Рус кишлак МФЮ, Улица Рус кишлак, Дом-11</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
@@ -21066,7 +21126,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>+998 87 561-52-96</t>
+          <t>+998 87 561-52-96 / +998 77 232-28-78 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr"/>
@@ -21092,7 +21152,7 @@
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>китоб, китоб МФЯ, гулустон кучаси, 90.0</t>
+          <t>китоб, китоб МФЯ, гулустон кучаси, 90-uy</t>
         </is>
       </c>
       <c r="G81" s="9" t="inlineStr">
@@ -21123,12 +21183,12 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Bogʻishamol MFY, Qorapoycha, 6 uy</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>+998 88 865-90-08</t>
+          <t>+998 88 981-83-80</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr"/>
@@ -21216,7 +21276,7 @@
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog', Kenguzar MFY, Chig'atoy, 6.0</t>
+          <t>Yakkabog', Kenguzar MFY, Chig'atoy, 6-uy</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
@@ -21247,7 +21307,7 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Xoji MFY, Uzunqir kuchasi, 106.0</t>
+          <t>Kitob tumani, Xoji MFY, Uzunqir kuchasi, 106-uy</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -21283,7 +21343,7 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>+998 97 960-25-35</t>
+          <t>+998 97 960-25-35 / +998 91 216-23-04 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr"/>
@@ -21309,7 +21369,7 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Kichik novqat mfy, Soyboʻyi koʻchasi, 04</t>
+          <t>Shahrisabz tumani, Maktobod mfy, Soyboʻyi koʻchasi, 4-uy</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -21335,17 +21395,17 @@
       </c>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Quruqsoy MFY, Buzovut qishlogʻi, 111-uy</t>
         </is>
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>+998 93 019-06-86</t>
+          <t>+998 70 331-87-08</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr"/>
@@ -21371,12 +21431,12 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Nomozgoh MFY, Taragʻay Bahodir, 2.31-uy</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>+998 91 948-38-79</t>
+          <t>+998 87 926-61-08</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr"/>
@@ -21464,7 +21524,7 @@
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Yakkabogʻ tumani, Alakuylak MFY, Hamid Olimjon koʻchasi, 55.0</t>
+          <t>Yakkabogʻ tumani, Alakuylak MFY, Hamid Olimjon koʻchasi, 55-uy</t>
         </is>
       </c>
       <c r="G93" s="9" t="inlineStr">
@@ -21500,7 +21560,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>+998 99 153-48-38</t>
+          <t>+998 99 153-48-38 / +998 70 034-22-44 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H94" s="4" t="inlineStr"/>
@@ -21557,12 +21617,12 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Katlos MFY, Bogʻiston kòchasi, 28-uy</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>+998 91 005-49-08</t>
+          <t>+998 88 205-49-08</t>
         </is>
       </c>
       <c r="H96" s="4" t="inlineStr"/>
@@ -21588,7 +21648,7 @@
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, Guliston  MFY, Qoʻshtepa kòchasi, 329.0</t>
+          <t>Shahrisabz shahar, Guliston MFY, Qoʻshtepa kòchasi, 329-uy</t>
         </is>
       </c>
       <c r="G97" s="9" t="inlineStr">
@@ -21681,7 +21741,7 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Iskana MFY, Uchtepalik, 52.0</t>
+          <t>Kitob tumani, Iskana MFY, Uchtepalik, 52-uy</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -21805,7 +21865,7 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49.0</t>
+          <t>Kitob tumani, Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49-uy</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -21867,10 +21927,14 @@
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G106" s="4" t="inlineStr"/>
+          <t>Shahrisabz tumani, Abziyat MFY, Hidoyat ko’chasi, 1-uy</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>+998 93 804-18-14</t>
+        </is>
+      </c>
       <c r="H106" s="4" t="inlineStr"/>
     </row>
     <row r="107" ht="20" customHeight="1">
@@ -21894,7 +21958,7 @@
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Xitoy MFY, Besh chinor, 65.0</t>
+          <t>Shahrisabz tuman, Xitoy MFY, Besh chinor, 65-uy</t>
         </is>
       </c>
       <c r="G107" s="9" t="inlineStr">
@@ -21987,7 +22051,7 @@
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guliston MFY, Qo'shtepa mahallasi, 75.0</t>
+          <t>Kitob tumani, Guliston MFY, Qo'shtepa mahallasi, 75-uy</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -22142,12 +22206,12 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Chiroqchi MFY, Elabot kuchasi, 227-uy</t>
         </is>
       </c>
       <c r="G115" s="9" t="inlineStr">
         <is>
-          <t>+998 97 676-09-05</t>
+          <t>+998 97 787-47-95</t>
         </is>
       </c>
       <c r="H115" s="9" t="inlineStr"/>
@@ -22204,7 +22268,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Xalqlar do'stligi MFY, Qashqadaryo2, 65.0</t>
+          <t>Kitob tumani, Xalqlar do'stligi MFY, Qashqadaryo2, 65-uy</t>
         </is>
       </c>
       <c r="G117" s="9" t="inlineStr">
@@ -22235,7 +22299,7 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Qumqishloq MFY, Hoji koʻchasi, 2-uy</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -22292,17 +22356,17 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Taragʻay MFY, Taragʻay, Yuq</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>+998 91 871-57-37</t>
+          <t>+998 77 006-91-49</t>
         </is>
       </c>
       <c r="H120" s="4" t="inlineStr"/>
@@ -22364,7 +22428,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>+998 87 636-07-08</t>
+          <t>+998 87 636-07-08 / +998 97 636-37-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr"/>
@@ -22488,7 +22552,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>+998 88 100-95-04</t>
+          <t>+998 88 100-95-04 / +998 97 632-55-74 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr"/>
@@ -22514,12 +22578,12 @@
       </c>
       <c r="F127" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Toʻdamaydon, Fidokor, 92.0</t>
+          <t>Shahrisabz tumani, Toʻdamaydon, Fidokor, 92-uy</t>
         </is>
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>+998 77 629-45-08</t>
+          <t>+998 95 740-19-81</t>
         </is>
       </c>
       <c r="H127" s="9" t="inlineStr"/>
@@ -22545,12 +22609,12 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob, Iksana MFY, Iskana qishloqi, 40-uy</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>+998 88 619-97-03</t>
+          <t>+998 87 629-51-08</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr"/>
@@ -22576,12 +22640,12 @@
       </c>
       <c r="F129" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, BektimirMFY, Yoshlar kuchasi, 27-uy</t>
         </is>
       </c>
       <c r="G129" s="9" t="inlineStr">
         <is>
-          <t>+998 93 636-79-86</t>
+          <t>+998 87 934-76-08</t>
         </is>
       </c>
       <c r="H129" s="9" t="inlineStr"/>
@@ -22607,12 +22671,12 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Beshariq MFY, Mehrobod, 45-uy</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>+998 97 618-02-59</t>
+          <t>+998 77 818-18-56</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr"/>
@@ -22638,7 +22702,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Katlos mfy, Obigarm kuchasi, 89.0</t>
+          <t>Kitob tumani, Katlos mfy, Obigarm kuchasi, 89-uy</t>
         </is>
       </c>
       <c r="G131" s="9" t="inlineStr">
@@ -22700,7 +22764,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Oqsuv MFY, Nimgi qishloq, 152-uy</t>
         </is>
       </c>
       <c r="G133" s="9" t="inlineStr">
@@ -22762,7 +22826,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Miraki mfy, Navoiy ko'chasi, 68.0</t>
+          <t>Shahrisabz tumani, Miraki mfy, Navoiy ko'chasi, 68-uy</t>
         </is>
       </c>
       <c r="G135" s="9" t="inlineStr">
@@ -22793,12 +22857,12 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrissbz tumani, Zangi, Keldihayot koʻchasi 290, 290-uy</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>+998 70 188-54-32</t>
+          <t>+998 77 838-07-48</t>
         </is>
       </c>
       <c r="H136" s="4" t="inlineStr"/>
@@ -22824,7 +22888,7 @@
       </c>
       <c r="F137" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tuman, Hamid Olimjon, Zilol buloq, 17-uy</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
@@ -22855,7 +22919,7 @@
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Hamid Olimjon MFY, Amir Temur, 69.0</t>
+          <t>Kitob tumani, Hamid Olimjon MFY, Amir Temur, 69-uy</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -22917,12 +22981,12 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shaxresabiz tumani, Quchi MFY, Quchi kuchasi, 56-uy</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>+998 91 949-16-27</t>
+          <t>+998 90 069-89-98</t>
         </is>
       </c>
       <c r="H140" s="4" t="inlineStr"/>
@@ -22975,7 +23039,7 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Sayyod MFY, Obod mahallasi, 13.0</t>
+          <t>Shahrisabz tumani, Sayyod MFY, Obod mahallasi, 13-uy</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -23006,7 +23070,7 @@
       </c>
       <c r="F143" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Surum mahallasi, Sokin koʻchasi, 66.0</t>
+          <t>Kitob tumani, Surum mahallasi, Sokin koʻchasi, 66-uy</t>
         </is>
       </c>
       <c r="G143" s="9" t="inlineStr">
@@ -23068,12 +23132,12 @@
       </c>
       <c r="F145" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Dustlik MFY, Bunyodkor kuchasi, 97-uy</t>
         </is>
       </c>
       <c r="G145" s="9" t="inlineStr">
         <is>
-          <t>+998 90 894-24-71</t>
+          <t>+998 90 864-24-71</t>
         </is>
       </c>
       <c r="H145" s="9" t="inlineStr"/>
@@ -23130,7 +23194,7 @@
       </c>
       <c r="F147" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Jilisuv MFY, Yangi Jilisuv, 99.0</t>
+          <t>Kitob tumani, Jilisuv MFY, Yangi Jilisuv, 99-uy</t>
         </is>
       </c>
       <c r="G147" s="9" t="inlineStr">
@@ -23285,12 +23349,12 @@
       </c>
       <c r="F152" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saray MFY, Yangiqishloq, 81-uy</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>+998 90 341-06-76</t>
+          <t>+998 91 898-04-95</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr"/>
@@ -23347,7 +23411,7 @@
       </c>
       <c r="F154" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shaxar, Kesh mahalas, Kalakon kuchas, 73-uy</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -23440,7 +23504,7 @@
       </c>
       <c r="F157" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog‘ tumani, Darxon MFY, Eshonguzar, 52-uy</t>
+          <t>Shahrisabz tumani, Darxon MFY, Eshonguzar kôchasi, 52-uy</t>
         </is>
       </c>
       <c r="G157" s="9" t="inlineStr">
@@ -23471,10 +23535,14 @@
       </c>
       <c r="F158" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="inlineStr"/>
+          <t>Shahrisabz Shahar, Farovon, Farovon kuchasi, 14-uy</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 562-65-77</t>
+        </is>
+      </c>
       <c r="H158" s="4" t="inlineStr"/>
     </row>
     <row r="159" ht="20" customHeight="1">
@@ -23498,12 +23566,12 @@
       </c>
       <c r="F159" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shaxar, Sinabog MFY, oqshom, 112-uy</t>
         </is>
       </c>
       <c r="G159" s="9" t="inlineStr">
         <is>
-          <t>+998 91 952-43-44</t>
+          <t>+998 77 810-82-80</t>
         </is>
       </c>
       <c r="H159" s="9" t="inlineStr"/>
@@ -23565,7 +23633,7 @@
       </c>
       <c r="G161" s="9" t="inlineStr">
         <is>
-          <t>+998 70 034-95-05</t>
+          <t>+998 70 034-95-05 / +998 99 468-84-06 (Otasi / Onasi)</t>
         </is>
       </c>
       <c r="H161" s="9" t="inlineStr"/>
@@ -23591,7 +23659,7 @@
       </c>
       <c r="F162" s="7" t="inlineStr">
         <is>
-          <t>Kitob tuman, Katlos MFY, Oshqon kuchasi, 69-uy</t>
+          <t>Kitob tumani, Katlos MFY, Oshqon, 69-uy</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -23653,7 +23721,7 @@
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Sariosiyo MFY, Chinorlik ko'chasi, 14.0</t>
+          <t>Kitob tumani, Sariosiyo MFY, Chinorlik koʻchasi, 14-uy</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -23684,7 +23752,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Ulugʻbek MFY, Qizil darvoza kuchasi, 116.0</t>
+          <t>Kitob tumani, Ulugʻbek MFY, Qizil darvoza kuchasi, 116-uy</t>
         </is>
       </c>
       <c r="G165" s="9" t="inlineStr">
@@ -23710,17 +23778,17 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi, Hamid olimjon MFY, Haytkul, 115-uy</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
         <is>
-          <t>+998 91 217-14-30</t>
+          <t>+998 88 244-68-08</t>
         </is>
       </c>
       <c r="H166" s="4" t="inlineStr"/>
@@ -23866,10 +23934,14 @@
       </c>
       <c r="F171" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G171" s="9" t="inlineStr"/>
+          <t>Shahrisabz tumani, Xujahurason mahalla, Sugʻdiyona, 50-uy</t>
+        </is>
+      </c>
+      <c r="G171" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 386-56-12</t>
+        </is>
+      </c>
       <c r="H171" s="9" t="inlineStr"/>
     </row>
     <row r="172" ht="20" customHeight="1">
@@ -23893,7 +23965,7 @@
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>Kitob  rayon, Oqsuv MFY, Nimgi qishloq, 38_uy</t>
+          <t>Kitob tumani, Oqsuv, Nimgi qishloq, 38-uy</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -23924,7 +23996,7 @@
       </c>
       <c r="F173" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Miraki mahallasi, Navoiy, 84 uy</t>
+          <t>Miraki, Alisher Navoiy, Navoiy kuchasi, 84 uy</t>
         </is>
       </c>
       <c r="G173" s="9" t="inlineStr">
@@ -23955,7 +24027,7 @@
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Yomchi, Abdulqosim Firdavsiy, 134-uy</t>
+          <t>Shahrisabz tumani, Q9oʻrgʻon tepa MFY, Abdulqodimfirdavsiy koʻchasi, 134-uy</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -23986,7 +24058,7 @@
       </c>
       <c r="F175" s="12" t="inlineStr">
         <is>
-          <t>Qamashi, Yuksalish MFY, Olmazor, 124.0</t>
+          <t>Qamashi tumani, Yuksalish MFY, Olmazor koʻchasi, 124-uy</t>
         </is>
       </c>
       <c r="G175" s="9" t="inlineStr">
@@ -24048,7 +24120,7 @@
       </c>
       <c r="F177" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Yashil diyor mfy, Yashil diyor kuchasi, 118.0</t>
+          <t>Shahrisabz shahri, Yashil diyor 116, Yashil diyor kuchasi, 118 uy</t>
         </is>
       </c>
       <c r="G177" s="9" t="inlineStr">
@@ -24079,7 +24151,7 @@
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>Shaxrisabz tumani, Meraki MFY, NAVOIY KÖCHASI, 48.0</t>
+          <t>Shaxrisabz tumani, Meraki MFY, NAVOIY KÖCHASI, 48-uy</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -24110,10 +24182,14 @@
       </c>
       <c r="F179" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G179" s="9" t="inlineStr"/>
+          <t>Shahrisabz tumani, Boston MFY, Kenagaz, 73- uy</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>+998 50 589-58-77</t>
+        </is>
+      </c>
       <c r="H179" s="9" t="inlineStr"/>
     </row>
     <row r="180" ht="20" customHeight="1">
@@ -24132,12 +24208,12 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkaboğ tumani, Yashnabod MFY, Faravon kochasi, 223-uy</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -24220,7 +24296,7 @@
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Uzoqova Fazilat Nurali qizi</t>
+          <t>Xolmurodova Sabina A'zam qizi</t>
         </is>
       </c>
       <c r="E183" s="9" t="inlineStr">
@@ -24230,12 +24306,12 @@
       </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
-          <t>Shaxrisabz tumani, Shamaton MFY, Yangiobod1, 111 uy</t>
+          <t>Shahrisabz shahar, Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
         </is>
       </c>
       <c r="G183" s="9" t="inlineStr">
         <is>
-          <t>+998 93 891-85-90</t>
+          <t>+998 90 881-06-10</t>
         </is>
       </c>
       <c r="H183" s="9" t="inlineStr"/>
@@ -24251,7 +24327,7 @@
       </c>
       <c r="D184" s="5" t="inlineStr">
         <is>
-          <t>Xolmurodova Sabina A'zam qizi</t>
+          <t>Yahyomurodova Gulsanam Akmal qizi</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
@@ -24261,12 +24337,12 @@
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, Fayzabod MFY, Quruvchilar ko'chasi, 73-uy</t>
+          <t>Kitob tumani, Oqsuv MFY, Nimgi qishlog'i, 156uy</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
         <is>
-          <t>+998 90 881-06-10</t>
+          <t>+998 77 371-00-28</t>
         </is>
       </c>
       <c r="H184" s="4" t="inlineStr"/>
@@ -24282,7 +24358,7 @@
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>Yahyomurodova Gulsanam Akmal qizi</t>
+          <t>Zarifova Marjona Samijon qizi</t>
         </is>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -24292,46 +24368,15 @@
       </c>
       <c r="F185" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Oqsuv MFY, Yoshlar kuchasi, 156-uy</t>
+          <t>Kiuob tumani, Ulubek MFY, Oʻrikzor koʻchasi, 23-uy</t>
         </is>
       </c>
       <c r="G185" s="9" t="inlineStr">
         <is>
-          <t>+998 77 371-00-28</t>
+          <t>+998 87 561-30-02</t>
         </is>
       </c>
       <c r="H185" s="9" t="inlineStr"/>
-    </row>
-    <row r="186" ht="20" customHeight="1">
-      <c r="B186" s="4" t="n">
-        <v>181</v>
-      </c>
-      <c r="C186" s="6" t="inlineStr">
-        <is>
-          <t>26-06</t>
-        </is>
-      </c>
-      <c r="D186" s="5" t="inlineStr">
-        <is>
-          <t>Zarifova Marjona Samijon qizi</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>O'z uyidan</t>
-        </is>
-      </c>
-      <c r="F186" s="7" t="inlineStr">
-        <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>+998 90 518-18-84</t>
-        </is>
-      </c>
-      <c r="H186" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24829,18 +24874,22 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>+998 90 878-81-08</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr"/>
+          <t>+998 70 066-73-09</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+998 70 390-23-08</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boston MFY, Abdulla Qodiriy köchasi, 31-uy</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -24880,7 +24929,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Duxchi MFY, Duxchi qishlog'i, 148.0</t>
+          <t>Shahrisabz tumani, Duxchi MFY, Duxchi qishlog'i, 148-uy</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -24915,12 +24964,12 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Dòstlik MFY, Dòstlik kuchasi, 19-uy</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -24948,15 +24997,19 @@
           <t>+998 91 224-00-18</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>+998 91 224-00-18</t>
+        </is>
+      </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Sinabog' M F Y, Sinabog' mahallasi, 101-uy</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -25076,7 +25129,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guluston, Guluston, 4.0</t>
+          <t>Kitob tumani, Guluston, Guluston, 4-uy</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -25104,15 +25157,19 @@
           <t>+998 77 062-98-90</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 319-62-60</t>
+        </is>
+      </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Opasi / Singlisi</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Kesh MFY, Kalakon kucha, 91-uy</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -25137,27 +25194,27 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>+998 88 617-78-60</t>
+          <t>+998 97 619-02-15</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>+998 91 457-78-60</t>
+          <t>+998 88 731-19-69</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Pakkandi MFY, Safarabot, 29_uy</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -25297,22 +25354,22 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>+998 97 335-05-82</t>
+          <t>+998 97 863-50-82</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>+998 97 863-50-82</t>
+          <t>+998 97 355-05-82</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Ukasi</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Yangiqishloq, 44-uy</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -25377,18 +25434,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>+998 77 864-19-17</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>+998 91 217-43-55</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Turon MFY, Yangi obod, 62-uy</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -25418,17 +25479,17 @@
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>+998 91 815-13-09</t>
+          <t>+998 91 817-20-73</t>
         </is>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Saroy MFY, Saroy koʻchasi, 17-uy</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -25456,15 +25517,19 @@
           <t>+998 88 088-01-24</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 561-30-02</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kotob tumani, Sevaz MFY, Taraqqiyot kuchasi, 130-uy</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -25504,7 +25569,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44.0</t>
+          <t>Qizil tepa, Yuksalish mfy, Roxat koʻchasi, 44-uy</t>
         </is>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -25544,7 +25609,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35.0</t>
+          <t>Kitob tumani, Palandara MFY, Oftobroʻya qishlogʻi, 35-uy</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -25755,21 +25820,29 @@
           <t>16.08.2008</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>+998 95 050-54-08</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+998 99 062-62-08</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Qamashi, Yuksalish MFY, Olmazor, 183-uy</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -25903,8 +25976,16 @@
           <t>13.11.2008</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>+998 50 002-60-78</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -25912,7 +25993,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Qashqadaryo MFY, Minjir qishlogʻi, 51-uy</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -25952,7 +26033,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz Shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
+          <t>Shahrisabz shahar, Ipak yo’li, Ipak yo’li, 118/28</t>
         </is>
       </c>
       <c r="I29" s="9" t="inlineStr">
@@ -25992,7 +26073,7 @@
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432.0</t>
+          <t>Kitob tumani, Zarafshon MFY, Yangiobod shaharchasi, 432-uy</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -26017,22 +26098,22 @@
       </c>
       <c r="E31" s="9" t="inlineStr">
         <is>
-          <t>+998 88 868-99-08</t>
+          <t>+998 88 336-77-74</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
         <is>
-          <t>+998 95 770-11-69</t>
+          <t>+998 90 716-31-42</t>
         </is>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Shanbe MFY, Shabboda, 35 -uy</t>
+          <t>Shahrisabz shahar, Do'stlik MFY, Bunyodkor ko'chasi, 62/16-uy</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -26060,7 +26141,11 @@
           <t>+998 88 011-58-19</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>+998 87 465-05-87</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -26068,7 +26153,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Boģbon MFY, Ochamayli kòchasi, 100-uy</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -26228,7 +26313,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84.0</t>
+          <t>Shahrisabz shahar, G'arov, G'arov kuchasi, 84-uy</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -26338,22 +26423,22 @@
       </c>
       <c r="F39" s="9" t="inlineStr">
         <is>
-          <t>+998 88 977-06-93</t>
+          <t>+998 99 201-92-74</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Ayoqchi MFY, Qovchin qishlogʻi, 92uy</t>
         </is>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -26528,20 +26613,24 @@
           <t>+998 91 709-08-76</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+998 91 812-76-97</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Yakkabogʻ tumani, Tatar MFY, Yangi hayot koʻchasi, 49_uy</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -26601,14 +26690,10 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>+998 95 259-06-25</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>+998 99 152-33-71</t>
-        </is>
-      </c>
+          <t>+998 95 259-06-25 / +998 99 152-33-71 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -26641,14 +26726,10 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>+998 87 358-87-97</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>+998 88 632-19-72</t>
-        </is>
-      </c>
+          <t>+998 87 358-87-97 / +998 88 632-19-72 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr"/>
       <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -26681,22 +26762,22 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>+998 99 943-05-96</t>
+          <t>+998 95 939-92-05</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>+998 95 939-92-05</t>
+          <t>+998 95 233-27-66</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Gelon MFY, Gelon, 43uy</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -26761,14 +26842,10 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>+998 88 803-91-93</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>+998 88 726-14-12</t>
-        </is>
-      </c>
+          <t>+998 88 803-91-93 / +998 88 726-14-12 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -26960,7 +27037,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Oq Oltin MFY, Al- Xorazmiy, 212.0</t>
+          <t>Shahrisabz tumani, Oq Oltin MFY, Al- Xorazmiy, 212-uy</t>
         </is>
       </c>
       <c r="I19" s="9" t="inlineStr">
@@ -26985,14 +27062,10 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>+998 87 392-00-25</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>+998 87 392-00-21</t>
-        </is>
-      </c>
+          <t>+998 87 392-00-25 / +998 87 392-00-21 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -27040,7 +27113,7 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Shahrizabz tumani, Turon MFY, Turon koʻchasi, 52.0</t>
+          <t>Shahrizabz tumani, Turon MFY, Turon koʻchasi, 52-uy</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -27187,12 +27260,12 @@
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Bunyodkor, Alpomish, 13-uy</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -27272,7 +27345,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Yakkabogʼ, Chagʼatoy, Yuq, 76.0</t>
+          <t>Yakkabogʼ, Chagʼatoy, Yuq, 76-uy</t>
         </is>
       </c>
       <c r="I27" s="9" t="inlineStr">
@@ -27312,7 +27385,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabiz tumani, Sanam MFY, Uzumzor kochasi, 60.0</t>
+          <t>Shahrisabiz tumani, Sanam MFY, Uzumzor kochasi, 60-uy</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -27420,15 +27493,19 @@
           <t>+998 88 761-13-10</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>+998 97 389-82-04</t>
+        </is>
+      </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Китабский район, Рус кишлак МФЮ, Улица Рус кишлак, Дом-11</t>
         </is>
       </c>
       <c r="I31" s="9" t="inlineStr">
@@ -27453,14 +27530,10 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>+998 87 561-52-96</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>+998 77 232-28-78</t>
-        </is>
-      </c>
+          <t>+998 87 561-52-96 / +998 77 232-28-78 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -27508,7 +27581,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>китоб, китоб МФЯ, гулустон кучаси, 90.0</t>
+          <t>китоб, китоб МФЯ, гулустон кучаси, 90-uy</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -27533,22 +27606,22 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>+998 88 865-90-08</t>
+          <t>+998 88 981-83-80</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>+998 88 186-17-12</t>
+          <t>+998 88 386-17-12</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Bogʻishamol MFY, Qorapoycha, 6 uy</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -27668,7 +27741,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Yakkabog', Kenguzar MFY, Chig'atoy, 6.0</t>
+          <t>Yakkabog', Kenguzar MFY, Chig'atoy, 6-uy</t>
         </is>
       </c>
       <c r="I37" s="9" t="inlineStr">
@@ -27708,7 +27781,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Xoji MFY, Uzunqir kuchasi, 106.0</t>
+          <t>Kitob tumani, Xoji MFY, Uzunqir kuchasi, 106-uy</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -27733,14 +27806,10 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>+998 97 960-25-35</t>
-        </is>
-      </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>+998 91 216-23-04</t>
-        </is>
-      </c>
+          <t>+998 97 960-25-35 / +998 91 216-23-04 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr"/>
       <c r="G39" s="9" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -27858,7 +27927,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>+998 87 607-82-87</t>
+          <t>+998 88 607-82-87</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -27868,7 +27937,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani, Kichik novqat mfy, Soyboʻyi koʻchasi, 04</t>
+          <t>Shahrisabz tumani, Maktobod mfy, Soyboʻyi koʻchasi, 4-uy</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -27893,10 +27962,14 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>+998 93 019-06-86</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr"/>
+          <t>+998 70 331-87-08</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>+998 70 119-06-86</t>
+        </is>
+      </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -27904,12 +27977,12 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Quruqsoy MFY, Buzovut qishlogʻi, 111-uy</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>O'z uyidan</t>
+          <t>Ijaradan</t>
         </is>
       </c>
     </row>
@@ -27929,22 +28002,22 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
+          <t>+998 87 926-61-08</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
           <t>+998 91 948-38-79</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>+998 88 596-71-79</t>
-        </is>
-      </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz shahar, Nomozgoh MFY, Taragʻay Bahodir, 2.31-uy</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -28064,7 +28137,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Yakkabogʻ tumani, Alakuylak MFY, Hamid Olimjon koʻchasi, 55.0</t>
+          <t>Yakkabogʻ tumani, Alakuylak MFY, Hamid Olimjon koʻchasi, 55-uy</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -28089,14 +28162,10 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>+998 99 153-48-38</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>+998 70 034-22-44</t>
-        </is>
-      </c>
+          <t>+998 99 153-48-38 / +998 70 034-22-44 (Otasi / Onasi)</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Otasi / Onasi</t>
@@ -28169,22 +28238,22 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>+998 91 005-49-08</t>
+          <t>+998 88 205-49-08</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>+998 93 553-33-51</t>
+          <t>+998 88 753-33-51</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Turmush o'rtog'i</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Katlos MFY, Bogʻiston kòchasi, 28-uy</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -28224,7 +28293,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz shahar, Guliston  MFY, Qoʻshtepa kòchasi, 329.0</t>
+          <t>Shahrisabz shahar, Guliston MFY, Qoʻshtepa kòchasi, 329-uy</t>
         </is>
       </c>
       <c r="I15" s="9" t="inlineStr">
@@ -28344,7 +28413,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Iskana MFY, Uchtepalik, 52.0</t>
+          <t>Kitob tumani, Iskana MFY, Uchtepalik, 52-uy</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -28504,7 +28573,7 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49.0</t>
+          <t>Kitob tumani, Uluğbek MFY, Mirzo Tursunzoda kòchasi, 49-uy</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -28567,16 +28636,24 @@
           <t>22.08.2008</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>+998 93 804-18-14</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>+998 97 385-83-69</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Abziyat MFY, Hidoyat ko’chasi, 1-uy</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -28616,7 +28693,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tuman, Xitoy MFY, Besh chinor, 65.0</t>
+          <t>Shahrisabz tuman, Xitoy MFY, Besh chinor, 65-uy</t>
         </is>
       </c>
       <c r="I25" s="9" t="inlineStr">
@@ -28732,7 +28809,7 @@
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Kitob tumani, Guliston MFY, Qo'shtepa mahallasi, 75.0</t>
+          <t>Kitob tumani, Guliston MFY, Qo'shtepa mahallasi, 75-uy</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -28917,22 +28994,22 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>+998 97 676-09-05</t>
+          <t>+998 97 787-47-95</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
         <is>
-          <t>+998 87 631-73-71</t>
+          <t>+998 97 697-95-92</t>
         </is>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Onasi</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Chiroqchi tumani, Chiroqchi MFY, Elabot kuchasi, 227-uy</t>
         </is>
       </c>
       <c r="I33" s="9" t="inlineStr">
@@ -29012,7 +29089,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Kitob tumani, Xalqlar do'stligi MFY, Qashqadaryo2, 65.0</t>
+          <t>Kitob tumani, Xalqlar do'stligi MFY, Qashqadaryo2, 65-uy</t>
         </is>
       </c>
       <c r="I35" s="9" t="inlineStr">
@@ -29042,17 +29119,17 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>+998 97 619-84-84</t>
+          <t>+998 97 387-87-37</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Otasi</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Shahrisabz tumani, Qumqishloq MFY, Hoji koʻchasi, 2-uy</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">

--- a/hisobotlar/Davomat_Jurnali_Uchun_Malumotlar.xlsx
+++ b/hisobotlar/Davomat_Jurnali_Uchun_Malumotlar.xlsx
@@ -6606,7 +6606,11 @@
           <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>+998 99 217-47-52</t>
+        </is>
+      </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>T-40/2 02.09.2026</t>
@@ -11154,7 +11158,7 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Alaqo'yliq MFY, Mevali ko'chasi, 109-uy</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -15714,8 +15718,16 @@
           <t>Niyozova Komila Toshpulatovna</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr"/>
-      <c r="F64" s="4" t="inlineStr"/>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Turmush o'rtog'i</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>+998 95 528-40-81</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -20633,10 +20645,14 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr"/>
+          <t>Kitob tumani, Alaqo'yliq MFY, Mevali ko'chasi, 109-uy</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>+998 99 217-47-52</t>
+        </is>
+      </c>
       <c r="H64" s="4" t="inlineStr"/>
     </row>
     <row r="65" ht="20" customHeight="1">
@@ -26908,16 +26924,24 @@
           <t>24.05.1983</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>+998 99 217-47-52</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+998 95 528-40-81</t>
+        </is>
+      </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Otasi / Onasi</t>
+          <t>Turmush o'rtog'i</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>Shahrisabz tumani</t>
+          <t>Kitob tumani, Alaqo'yliq MFY, Mevali ko'chasi, 109-uy</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
